--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
